--- a/任务分配表.xlsx
+++ b/任务分配表.xlsx
@@ -42,6 +42,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>成员</t>
     </r>
     <r>
@@ -60,16 +65,250 @@
     <t>数据库、Feed CRUD、Feed Sync、OPML I/O、CI/CD</t>
   </si>
   <si>
-    <t>`store/db.py`: SQLite WAL 模式连接管理、Schema 定义及迁移
-`store/migrations.py`: 版本化迁移管理器
-`core/feed/parser.py`: feedparser 异步封装，返回 FeedData dataclass
-`core/feed/sync.py`: 并发同步逻辑与增量更新（asyncio.Semaphore）
-`core/feed/opml.py`: OPML 格式导入导出
-`store/feed_store.py`: Feed 订阅源 CRUD 数据访问层
-`store/entry_store.py`: 文章 CRUD + 查询数据访问层
-`store/content_store.py`: Reader 管线缓存持久化
-`app/state.py`: 全局状态管理 AppState dataclass
-`tests/` &amp; `.github/workflows/ci.yml`: 单元测试框架及 CI 配置</t>
+    <r>
+      <t xml:space="preserve">`store/db.py`: SQLite WAL </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模式连接管理、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Schema </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>定义及迁移</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`store/migrations.py`: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>版本化迁移管理器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`core/feed/parser.py`: feedparser </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>异步封装，返回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> FeedData dataclass
+`core/feed/sync.py`: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并发同步逻辑与增量更新（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t>asyncio.Semaphore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`core/feed/opml.py`: OPML </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>格式导入导出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`store/feed_store.py`: Feed </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>订阅源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据访问层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`store/entry_store.py`: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文章</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> CRUD + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>查询数据访问层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`store/content_store.py`: Reader </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>管线缓存持久化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+`app/state.py`: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全局状态管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> AppState dataclass
+`tests/` &amp; `.github/workflows/ci.yml`: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元测试框架及</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Alibaba PuHuiTi 2.0"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> CI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>配置</t>
+    </r>
   </si>
   <si>
     <t>成员 B</t>
